--- a/data/dividends_info_20261012.xlsx
+++ b/data/dividends_info_20261012.xlsx
@@ -710,12 +710,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>45.56499862670898</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1975200322890922</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>63</v>
       </c>
@@ -1368,12 +1364,8 @@
           <t>IT0003132476</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>25.40500068664551</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.062782888023811</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>-21</v>
       </c>
@@ -1462,12 +1454,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>45.56499862670898</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1975200322890922</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>-21</v>
       </c>
@@ -3337,7 +3325,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3347,14 +3335,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3364,7 +3352,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3376,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3398,14 +3386,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3415,14 +3403,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3439,7 +3427,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3456,7 +3444,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3473,7 +3461,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3490,7 +3478,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3507,7 +3495,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3524,7 +3512,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3585,14 +3573,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3602,14 +3590,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3619,14 +3607,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3636,14 +3624,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3653,14 +3641,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3677,7 +3665,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3694,7 +3682,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3711,7 +3699,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3728,7 +3716,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3738,14 +3726,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3762,7 +3750,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3779,7 +3767,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3796,7 +3784,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3813,7 +3801,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3830,7 +3818,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3847,7 +3835,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3864,7 +3852,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3874,14 +3862,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3898,7 +3886,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3915,7 +3903,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3932,7 +3920,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3942,14 +3930,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3966,7 +3954,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3976,14 +3964,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3993,14 +3981,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4017,7 +4005,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4027,14 +4015,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4051,7 +4039,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4061,14 +4049,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4078,14 +4066,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4119,7 +4107,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4136,7 +4124,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4146,7 +4134,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4175,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4204,7 +4192,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4221,7 +4209,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4231,14 +4219,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4255,7 +4243,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4272,7 +4260,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4289,7 +4277,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4299,14 +4287,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4316,7 +4304,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4328,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4350,14 +4338,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4367,14 +4355,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4384,14 +4372,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4408,7 +4396,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4418,14 +4406,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4442,7 +4430,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4459,7 +4447,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4476,7 +4464,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4486,14 +4474,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4510,7 +4498,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4527,7 +4515,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4544,7 +4532,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4554,14 +4542,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4578,7 +4566,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4595,7 +4583,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4612,7 +4600,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4629,7 +4617,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4646,7 +4634,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4663,7 +4651,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4680,7 +4668,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4697,7 +4685,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4707,14 +4695,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4731,7 +4719,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4741,14 +4729,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4758,14 +4746,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4775,14 +4763,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4792,14 +4780,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4816,7 +4804,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4833,7 +4821,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4850,7 +4838,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4860,14 +4848,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4884,7 +4872,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4894,14 +4882,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4911,14 +4899,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4935,7 +4923,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4952,7 +4940,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4969,7 +4957,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4979,14 +4967,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5003,7 +4991,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5013,14 +5001,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5030,14 +5018,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5054,7 +5042,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5071,7 +5059,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5088,7 +5076,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5126,639 +5114,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Avio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CALEFFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ESAUTOMOTION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Enervit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>GEOX S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GEOX S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>GVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HERA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>IREN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RCS MediaGroup S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sicily by Car S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Technoprobe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ZEST S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>